--- a/plots/countries/sectors/Morocco-sectors.xlsx
+++ b/plots/countries/sectors/Morocco-sectors.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t xml:space="preserve">Author</t>
   </si>
@@ -30,13 +30,7 @@
     <t xml:space="preserve">Data sources</t>
   </si>
   <si>
-    <t xml:space="preserve">Lamb, W. F. (2025). Tidy GHG Inventories (1.0) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14945466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">See also</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.5281/zenodo.14512139</t>
+    <t xml:space="preserve">Lamb, W. F. (2026). Tidy GHG Inventories (v2) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14512139</t>
   </si>
   <si>
     <t xml:space="preserve">country</t>
@@ -443,14 +437,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -464,39 +450,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>11</v>
-      </c>
-      <c r="E1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
         <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
       </c>
       <c r="D2" t="n">
         <v>2010</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F2" t="n">
         <v>16.5122078425215</v>
@@ -504,19 +490,19 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
         <v>2010</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>8.13452508050358</v>
@@ -524,19 +510,19 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
         <v>2010</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
         <v>0.199654105223128</v>
@@ -544,19 +530,19 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
         <v>2010</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
         <v>7.27636678953932</v>
@@ -564,19 +550,19 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
         <v>2010</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
         <v>17.9761076549878</v>
@@ -584,19 +570,19 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
         <v>2010</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F7" t="n">
         <v>14.1782399697508</v>
@@ -604,19 +590,19 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
         <v>2010</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F8" t="n">
         <v>5.8704912</v>
@@ -624,19 +610,19 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D9" t="n">
         <v>2010</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F9" t="n">
         <v>-2.23898575108756</v>
@@ -644,19 +630,19 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
         <v>2010</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
         <v>4.97429465790378</v>
@@ -664,19 +650,19 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
         <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" t="s">
-        <v>16</v>
       </c>
       <c r="D11" t="n">
         <v>2012</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
         <v>17.1790943751815</v>
@@ -684,19 +670,19 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
         <v>2012</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F12" t="n">
         <v>8.95514758900094</v>
@@ -704,19 +690,19 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D13" t="n">
         <v>2012</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F13" t="n">
         <v>0.219161492718252</v>
@@ -724,19 +710,19 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D14" t="n">
         <v>2012</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F14" t="n">
         <v>8.42813883482797</v>
@@ -744,19 +730,19 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D15" t="n">
         <v>2012</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F15" t="n">
         <v>20.7746821868966</v>
@@ -764,19 +750,19 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D16" t="n">
         <v>2012</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F16" t="n">
         <v>15.2022039763864</v>
@@ -784,19 +770,19 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D17" t="n">
         <v>2012</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F17" t="n">
         <v>6.36864158</v>
@@ -804,19 +790,19 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D18" t="n">
         <v>2012</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F18" t="n">
         <v>-1.89303842487652</v>
@@ -824,19 +810,19 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D19" t="n">
         <v>2012</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F19" t="n">
         <v>5.22621409281865</v>
@@ -844,19 +830,19 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
         <v>14</v>
-      </c>
-      <c r="B20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" t="s">
-        <v>16</v>
       </c>
       <c r="D20" t="n">
         <v>2014</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F20" t="n">
         <v>18.011331150391</v>
@@ -864,19 +850,19 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D21" t="n">
         <v>2014</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F21" t="n">
         <v>9.54555966389317</v>
@@ -884,19 +870,19 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D22" t="n">
         <v>2014</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F22" t="n">
         <v>0.23287957684554</v>
@@ -904,19 +890,19 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D23" t="n">
         <v>2014</v>
       </c>
       <c r="E23" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F23" t="n">
         <v>7.30440958941461</v>
@@ -924,19 +910,19 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D24" t="n">
         <v>2014</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F24" t="n">
         <v>21.9144697688849</v>
@@ -944,19 +930,19 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D25" t="n">
         <v>2014</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F25" t="n">
         <v>15.9291808823986</v>
@@ -964,19 +950,19 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D26" t="n">
         <v>2014</v>
       </c>
       <c r="E26" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F26" t="n">
         <v>5.68750269</v>
@@ -984,19 +970,19 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D27" t="n">
         <v>2014</v>
       </c>
       <c r="E27" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F27" t="n">
         <v>-1.74781542660699</v>
@@ -1004,19 +990,19 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D28" t="n">
         <v>2014</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F28" t="n">
         <v>5.50485497100788</v>
@@ -1024,19 +1010,19 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" t="s">
         <v>14</v>
-      </c>
-      <c r="B29" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" t="s">
-        <v>16</v>
       </c>
       <c r="D29" t="n">
         <v>2016</v>
       </c>
       <c r="E29" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F29" t="n">
         <v>18.0563962498365</v>
@@ -1044,19 +1030,19 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D30" t="n">
         <v>2016</v>
       </c>
       <c r="E30" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F30" t="n">
         <v>10.2477489294138</v>
@@ -1064,19 +1050,19 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D31" t="n">
         <v>2016</v>
       </c>
       <c r="E31" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F31" t="n">
         <v>0.211586857175356</v>
@@ -1084,19 +1070,19 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D32" t="n">
         <v>2016</v>
       </c>
       <c r="E32" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F32" t="n">
         <v>6.75968415335815</v>
@@ -1104,19 +1090,19 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D33" t="n">
         <v>2016</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F33" t="n">
         <v>21.9756919853408</v>
@@ -1124,19 +1110,19 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D34" t="n">
         <v>2016</v>
       </c>
       <c r="E34" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F34" t="n">
         <v>17.5424300038815</v>
@@ -1144,19 +1130,19 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D35" t="n">
         <v>2016</v>
       </c>
       <c r="E35" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F35" t="n">
         <v>6.03844325</v>
@@ -1164,19 +1150,19 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D36" t="n">
         <v>2016</v>
       </c>
       <c r="E36" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F36" t="n">
         <v>-1.70406633634038</v>
@@ -1184,19 +1170,19 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D37" t="n">
         <v>2016</v>
       </c>
       <c r="E37" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F37" t="n">
         <v>5.79332079475981</v>
@@ -1204,19 +1190,19 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" t="s">
         <v>14</v>
-      </c>
-      <c r="B38" t="s">
-        <v>15</v>
-      </c>
-      <c r="C38" t="s">
-        <v>16</v>
       </c>
       <c r="D38" t="n">
         <v>2018</v>
       </c>
       <c r="E38" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F38" t="n">
         <v>19.7455061049306</v>
@@ -1224,19 +1210,19 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D39" t="n">
         <v>2018</v>
       </c>
       <c r="E39" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F39" t="n">
         <v>10.8186215504257</v>
@@ -1244,19 +1230,19 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D40" t="n">
         <v>2018</v>
       </c>
       <c r="E40" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F40" t="n">
         <v>0.221355918867621</v>
@@ -1264,19 +1250,19 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D41" t="n">
         <v>2018</v>
       </c>
       <c r="E41" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F41" t="n">
         <v>7.71821834214341</v>
@@ -1284,19 +1270,19 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D42" t="n">
         <v>2018</v>
       </c>
       <c r="E42" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F42" t="n">
         <v>23.7363117126148</v>
@@ -1304,19 +1290,19 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D43" t="n">
         <v>2018</v>
       </c>
       <c r="E43" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F43" t="n">
         <v>18.7173887361421</v>
@@ -1324,19 +1310,19 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D44" t="n">
         <v>2018</v>
       </c>
       <c r="E44" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F44" t="n">
         <v>5.60494424</v>
@@ -1344,19 +1330,19 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D45" t="n">
         <v>2018</v>
       </c>
       <c r="E45" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F45" t="n">
         <v>-1.81892127868409</v>
@@ -1364,19 +1350,19 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D46" t="n">
         <v>2018</v>
       </c>
       <c r="E46" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F46" t="n">
         <v>6.12796875401865</v>
@@ -1384,19 +1370,19 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" t="s">
         <v>14</v>
-      </c>
-      <c r="B47" t="s">
-        <v>15</v>
-      </c>
-      <c r="C47" t="s">
-        <v>16</v>
       </c>
       <c r="D47" t="n">
         <v>2020</v>
       </c>
       <c r="E47" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F47" t="n">
         <v>19.2928555667332</v>
@@ -1404,19 +1390,19 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D48" t="n">
         <v>2020</v>
       </c>
       <c r="E48" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F48" t="n">
         <v>11.1577134583775</v>
@@ -1424,19 +1410,19 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D49" t="n">
         <v>2020</v>
       </c>
       <c r="E49" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F49" t="n">
         <v>0.15798343426998</v>
@@ -1444,19 +1430,19 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C50" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D50" t="n">
         <v>2020</v>
       </c>
       <c r="E50" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F50" t="n">
         <v>6.87594135915849</v>
@@ -1464,19 +1450,19 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C51" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D51" t="n">
         <v>2020</v>
       </c>
       <c r="E51" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F51" t="n">
         <v>28.705539713046</v>
@@ -1484,19 +1470,19 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C52" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D52" t="n">
         <v>2020</v>
       </c>
       <c r="E52" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F52" t="n">
         <v>16.3553702137765</v>
@@ -1504,19 +1490,19 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D53" t="n">
         <v>2020</v>
       </c>
       <c r="E53" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F53" t="n">
         <v>5.0536472</v>
@@ -1524,19 +1510,19 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D54" t="n">
         <v>2020</v>
       </c>
       <c r="E54" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F54" t="n">
         <v>-1.99892619322751</v>
@@ -1544,19 +1530,19 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D55" t="n">
         <v>2020</v>
       </c>
       <c r="E55" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F55" t="n">
         <v>6.38248850261605</v>
@@ -1564,19 +1550,19 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" t="s">
         <v>14</v>
-      </c>
-      <c r="B56" t="s">
-        <v>15</v>
-      </c>
-      <c r="C56" t="s">
-        <v>16</v>
       </c>
       <c r="D56" t="n">
         <v>2021</v>
       </c>
       <c r="E56" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F56" t="n">
         <v>19.8237520968162</v>
@@ -1584,19 +1570,19 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D57" t="n">
         <v>2021</v>
       </c>
       <c r="E57" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F57" t="n">
         <v>11.6812198292347</v>
@@ -1604,19 +1590,19 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D58" t="n">
         <v>2021</v>
       </c>
       <c r="E58" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F58" t="n">
         <v>0.160630381674767</v>
@@ -1624,19 +1610,19 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D59" t="n">
         <v>2021</v>
       </c>
       <c r="E59" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F59" t="n">
         <v>7.41267012775711</v>
@@ -1644,19 +1630,19 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D60" t="n">
         <v>2021</v>
       </c>
       <c r="E60" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F60" t="n">
         <v>30.6445119581156</v>
@@ -1664,19 +1650,19 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D61" t="n">
         <v>2021</v>
       </c>
       <c r="E61" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F61" t="n">
         <v>19.1167695481066</v>
@@ -1684,19 +1670,19 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C62" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D62" t="n">
         <v>2021</v>
       </c>
       <c r="E62" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F62" t="n">
         <v>5.7161991</v>
@@ -1704,19 +1690,19 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C63" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D63" t="n">
         <v>2021</v>
       </c>
       <c r="E63" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F63" t="n">
         <v>-1.69307201401137</v>
@@ -1724,19 +1710,19 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C64" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D64" t="n">
         <v>2021</v>
       </c>
       <c r="E64" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F64" t="n">
         <v>6.49908781953948</v>
@@ -1744,19 +1730,19 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
+        <v>12</v>
+      </c>
+      <c r="B65" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" t="s">
         <v>14</v>
-      </c>
-      <c r="B65" t="s">
-        <v>15</v>
-      </c>
-      <c r="C65" t="s">
-        <v>16</v>
       </c>
       <c r="D65" t="n">
         <v>2022</v>
       </c>
       <c r="E65" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F65" t="n">
         <v>18.510615869688</v>
@@ -1764,19 +1750,19 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D66" t="n">
         <v>2022</v>
       </c>
       <c r="E66" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F66" t="n">
         <v>11.7245291956667</v>
@@ -1784,19 +1770,19 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C67" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D67" t="n">
         <v>2022</v>
       </c>
       <c r="E67" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F67" t="n">
         <v>0.0381694693346198</v>
@@ -1804,19 +1790,19 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D68" t="n">
         <v>2022</v>
       </c>
       <c r="E68" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F68" t="n">
         <v>6.4858766205303</v>
@@ -1824,19 +1810,19 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C69" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D69" t="n">
         <v>2022</v>
       </c>
       <c r="E69" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F69" t="n">
         <v>32.3728252260044</v>
@@ -1844,19 +1830,19 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C70" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D70" t="n">
         <v>2022</v>
       </c>
       <c r="E70" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F70" t="n">
         <v>17.9013125989483</v>
@@ -1864,19 +1850,19 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D71" t="n">
         <v>2022</v>
       </c>
       <c r="E71" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F71" t="n">
         <v>5.4112883</v>
@@ -1884,19 +1870,19 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C72" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D72" t="n">
         <v>2022</v>
       </c>
       <c r="E72" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F72" t="n">
         <v>-0.72880999677784</v>
@@ -1904,19 +1890,19 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C73" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D73" t="n">
         <v>2022</v>
       </c>
       <c r="E73" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F73" t="n">
         <v>6.67243553426522</v>

--- a/plots/countries/sectors/Morocco-sectors.xlsx
+++ b/plots/countries/sectors/Morocco-sectors.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Data sources</t>
   </si>
   <si>
-    <t xml:space="preserve">Lamb, W. F. (2026). Tidy GHG Inventories (v2) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14512139</t>
+    <t xml:space="preserve">Lamb, W. F. (2026). Tidy GHG Inventories (v2.1) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14512139</t>
   </si>
   <si>
     <t xml:space="preserve">country</t>
